--- a/21Club_Sept_CW1/DS/Attendance.xlsx
+++ b/21Club_Sept_CW1/DS/Attendance.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\Batches\21Club_Sept_CW1\DS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\21Club_Sept_CW1\DS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5EE3E04-1D1A-446F-8313-51BE4493192E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F46AD40-D1E7-4BD5-B7DB-6E280DC48090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="15">
   <si>
     <t>Vedant</t>
   </si>
@@ -58,6 +59,18 @@
   </si>
   <si>
     <t>Total Lectures conducted after 20 July</t>
+  </si>
+  <si>
+    <t>Total/130</t>
+  </si>
+  <si>
+    <t>Total/5</t>
+  </si>
+  <si>
+    <t>Test Marks</t>
+  </si>
+  <si>
+    <t>Test Marks/5</t>
   </si>
 </sst>
 </file>
@@ -376,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AB16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
@@ -384,14 +397,14 @@
     <col min="4" max="5" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="4.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="16" width="5.77734375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="20" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B1" s="1">
         <v>45437</v>
       </c>
@@ -423,61 +436,58 @@
         <v>45480</v>
       </c>
       <c r="L1" s="1">
-        <v>45486</v>
+        <v>45493</v>
       </c>
       <c r="M1" s="1">
-        <v>45487</v>
+        <v>45494</v>
       </c>
       <c r="N1" s="1">
-        <v>45493</v>
+        <v>45501</v>
       </c>
       <c r="O1" s="1">
-        <v>45494</v>
+        <v>45507</v>
       </c>
       <c r="P1" s="1">
-        <v>45501</v>
+        <v>45514</v>
       </c>
       <c r="Q1" s="1">
-        <v>45507</v>
+        <v>45521</v>
       </c>
       <c r="R1" s="1">
-        <v>45514</v>
+        <v>45522</v>
       </c>
       <c r="S1" s="1">
-        <v>45521</v>
+        <v>45528</v>
       </c>
       <c r="T1" s="1">
-        <v>45522</v>
+        <v>45535</v>
       </c>
       <c r="U1" s="1">
-        <v>45528</v>
+        <v>45536</v>
       </c>
       <c r="V1" s="1">
-        <v>45535</v>
+        <v>45542</v>
       </c>
       <c r="W1" s="1">
-        <v>45536</v>
+        <v>45543</v>
       </c>
       <c r="X1" s="1">
-        <v>45542</v>
+        <v>45549</v>
       </c>
       <c r="Y1" s="1">
-        <v>45543</v>
+        <v>45550</v>
       </c>
       <c r="Z1" s="1">
-        <v>45549</v>
+        <v>45556</v>
       </c>
       <c r="AA1" s="1">
-        <v>45550</v>
+        <v>45557</v>
       </c>
       <c r="AB1" s="1">
-        <v>45556</v>
-      </c>
-      <c r="AC1" s="1">
-        <v>45557</v>
+        <v>45591</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -511,6 +521,12 @@
       <c r="K2" t="s">
         <v>6</v>
       </c>
+      <c r="L2" t="s">
+        <v>5</v>
+      </c>
+      <c r="M2" t="s">
+        <v>5</v>
+      </c>
       <c r="N2" t="s">
         <v>5</v>
       </c>
@@ -518,10 +534,10 @@
         <v>5</v>
       </c>
       <c r="P2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R2" t="s">
         <v>8</v>
@@ -556,11 +572,8 @@
       <c r="AB2" t="s">
         <v>8</v>
       </c>
-      <c r="AC2" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -594,6 +607,12 @@
       <c r="K3" t="s">
         <v>7</v>
       </c>
+      <c r="L3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M3" t="s">
+        <v>6</v>
+      </c>
       <c r="N3" t="s">
         <v>6</v>
       </c>
@@ -604,7 +623,7 @@
         <v>6</v>
       </c>
       <c r="Q3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R3" t="s">
         <v>6</v>
@@ -616,7 +635,7 @@
         <v>6</v>
       </c>
       <c r="U3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V3" t="s">
         <v>6</v>
@@ -639,11 +658,8 @@
       <c r="AB3" t="s">
         <v>6</v>
       </c>
-      <c r="AC3" t="s">
-        <v>6</v>
-      </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -677,23 +693,29 @@
       <c r="K4" t="s">
         <v>7</v>
       </c>
+      <c r="L4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" t="s">
+        <v>5</v>
+      </c>
       <c r="N4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q4" t="s">
         <v>7</v>
       </c>
       <c r="R4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T4" t="s">
         <v>8</v>
@@ -722,11 +744,8 @@
       <c r="AB4" t="s">
         <v>8</v>
       </c>
-      <c r="AC4" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -760,6 +779,12 @@
       <c r="K5" t="s">
         <v>5</v>
       </c>
+      <c r="L5" t="s">
+        <v>6</v>
+      </c>
+      <c r="M5" t="s">
+        <v>6</v>
+      </c>
       <c r="N5" t="s">
         <v>6</v>
       </c>
@@ -767,13 +792,13 @@
         <v>6</v>
       </c>
       <c r="P5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S5" t="s">
         <v>5</v>
@@ -782,7 +807,7 @@
         <v>6</v>
       </c>
       <c r="U5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V5" t="s">
         <v>6</v>
@@ -791,25 +816,22 @@
         <v>6</v>
       </c>
       <c r="X5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z5" t="s">
         <v>5</v>
       </c>
       <c r="AA5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB5" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -843,11 +865,17 @@
       <c r="K6" t="s">
         <v>7</v>
       </c>
+      <c r="L6" t="s">
+        <v>6</v>
+      </c>
+      <c r="M6" t="s">
+        <v>6</v>
+      </c>
       <c r="N6" t="s">
         <v>6</v>
       </c>
       <c r="O6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P6" t="s">
         <v>6</v>
@@ -856,51 +884,111 @@
         <v>7</v>
       </c>
       <c r="R6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S6" t="s">
         <v>7</v>
       </c>
       <c r="T6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U6" t="s">
         <v>7</v>
       </c>
       <c r="V6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W6" t="s">
         <v>7</v>
       </c>
       <c r="X6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z6" t="s">
         <v>6</v>
       </c>
       <c r="AA6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M7" t="s">
+        <v>8</v>
+      </c>
+      <c r="N7" t="s">
+        <v>8</v>
+      </c>
+      <c r="O7" t="s">
+        <v>8</v>
+      </c>
+      <c r="P7" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>8</v>
+      </c>
+      <c r="R7" t="s">
+        <v>8</v>
+      </c>
+      <c r="S7" t="s">
+        <v>8</v>
+      </c>
+      <c r="T7" t="s">
+        <v>6</v>
+      </c>
+      <c r="U7" t="s">
+        <v>6</v>
+      </c>
       <c r="V7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W7" t="s">
         <v>6</v>
       </c>
       <c r="X7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y7" t="s">
         <v>6</v>
@@ -912,18 +1000,15 @@
         <v>6</v>
       </c>
       <c r="AB7" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
       <c r="K16">
         <v>22</v>
       </c>
@@ -933,5 +1018,871 @@
     <sortCondition ref="A2:A6"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4E9CCB6-06B9-4C9F-B983-8B43200B51F4}">
+  <dimension ref="A1:AF7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="4.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="20" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="27" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.5546875" customWidth="1"/>
+    <col min="29" max="29" width="9" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="7" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B1" s="1">
+        <v>45437</v>
+      </c>
+      <c r="C1" s="1">
+        <v>45438</v>
+      </c>
+      <c r="D1" s="1">
+        <v>45444</v>
+      </c>
+      <c r="E1" s="1">
+        <v>45445</v>
+      </c>
+      <c r="F1" s="1">
+        <v>45458</v>
+      </c>
+      <c r="G1" s="1">
+        <v>45459</v>
+      </c>
+      <c r="H1" s="1">
+        <v>45465</v>
+      </c>
+      <c r="I1" s="1">
+        <v>45466</v>
+      </c>
+      <c r="J1" s="1">
+        <v>45479</v>
+      </c>
+      <c r="K1" s="1">
+        <v>45480</v>
+      </c>
+      <c r="L1" s="1">
+        <v>45493</v>
+      </c>
+      <c r="M1" s="1">
+        <v>45494</v>
+      </c>
+      <c r="N1" s="1">
+        <v>45501</v>
+      </c>
+      <c r="O1" s="1">
+        <v>45507</v>
+      </c>
+      <c r="P1" s="1">
+        <v>45514</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>45521</v>
+      </c>
+      <c r="R1" s="1">
+        <v>45522</v>
+      </c>
+      <c r="S1" s="1">
+        <v>45528</v>
+      </c>
+      <c r="T1" s="1">
+        <v>45535</v>
+      </c>
+      <c r="U1" s="1">
+        <v>45536</v>
+      </c>
+      <c r="V1" s="1">
+        <v>45542</v>
+      </c>
+      <c r="W1" s="1">
+        <v>45543</v>
+      </c>
+      <c r="X1" s="1">
+        <v>45549</v>
+      </c>
+      <c r="Y1" s="1">
+        <v>45550</v>
+      </c>
+      <c r="Z1" s="1">
+        <v>45556</v>
+      </c>
+      <c r="AA1" s="1">
+        <v>45557</v>
+      </c>
+      <c r="AB1" s="1"/>
+      <c r="AC1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <f>_xlfn.IFS(Sheet1!B2="P", 5,Sheet1!B2="O", 3,Sheet1!B2="A",0,Sheet1!B2="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <f>_xlfn.IFS(Sheet1!C2="P", 5,Sheet1!C2="O", 3,Sheet1!C2="A",0,Sheet1!C2="-",0)</f>
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <f>_xlfn.IFS(Sheet1!D2="P", 5,Sheet1!D2="O", 3,Sheet1!D2="A",0,Sheet1!D2="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <f>_xlfn.IFS(Sheet1!E2="P", 5,Sheet1!E2="O", 3,Sheet1!E2="A",0,Sheet1!E2="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <f>_xlfn.IFS(Sheet1!F2="P", 5,Sheet1!F2="O", 3,Sheet1!F2="A",0,Sheet1!F2="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <f>_xlfn.IFS(Sheet1!G2="P", 5,Sheet1!G2="O", 3,Sheet1!G2="A",0,Sheet1!G2="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <f>_xlfn.IFS(Sheet1!H2="P", 5,Sheet1!H2="O", 3,Sheet1!H2="A",0,Sheet1!H2="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <f>_xlfn.IFS(Sheet1!I2="P", 5,Sheet1!I2="O", 3,Sheet1!I2="A",0,Sheet1!I2="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <f>_xlfn.IFS(Sheet1!J2="P", 5,Sheet1!J2="O", 3,Sheet1!J2="A",0,Sheet1!J2="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <f>_xlfn.IFS(Sheet1!K2="P", 5,Sheet1!K2="O", 3,Sheet1!K2="A",0,Sheet1!K2="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <f>_xlfn.IFS(Sheet1!L2="P", 5,Sheet1!L2="O", 3,Sheet1!L2="A",0,Sheet1!L2="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <f>_xlfn.IFS(Sheet1!M2="P", 5,Sheet1!M2="O", 3,Sheet1!M2="A",0,Sheet1!M2="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <f>_xlfn.IFS(Sheet1!N2="P", 5,Sheet1!N2="O", 3,Sheet1!N2="A",0,Sheet1!N2="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <f>_xlfn.IFS(Sheet1!O2="P", 5,Sheet1!O2="O", 3,Sheet1!O2="A",0,Sheet1!O2="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <f>_xlfn.IFS(Sheet1!P2="P", 5,Sheet1!P2="O", 3,Sheet1!P2="A",0,Sheet1!P2="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <f>_xlfn.IFS(Sheet1!Q2="P", 5,Sheet1!Q2="O", 3,Sheet1!Q2="A",0,Sheet1!Q2="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <f>_xlfn.IFS(Sheet1!R2="P", 5,Sheet1!R2="O", 3,Sheet1!R2="A",0,Sheet1!R2="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <f>_xlfn.IFS(Sheet1!S2="P", 5,Sheet1!S2="O", 3,Sheet1!S2="A",0,Sheet1!S2="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <f>_xlfn.IFS(Sheet1!T2="P", 5,Sheet1!T2="O", 3,Sheet1!T2="A",0,Sheet1!T2="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <f>_xlfn.IFS(Sheet1!U2="P", 5,Sheet1!U2="O", 3,Sheet1!U2="A",0,Sheet1!U2="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <f>_xlfn.IFS(Sheet1!V2="P", 5,Sheet1!V2="O", 3,Sheet1!V2="A",0,Sheet1!V2="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <f>_xlfn.IFS(Sheet1!W2="P", 5,Sheet1!W2="O", 3,Sheet1!W2="A",0,Sheet1!W2="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <f>_xlfn.IFS(Sheet1!X2="P", 5,Sheet1!X2="O", 3,Sheet1!X2="A",0,Sheet1!X2="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <f>_xlfn.IFS(Sheet1!Y2="P", 5,Sheet1!Y2="O", 3,Sheet1!Y2="A",0,Sheet1!Y2="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <f>_xlfn.IFS(Sheet1!Z2="P", 5,Sheet1!Z2="O", 3,Sheet1!Z2="A",0,Sheet1!Z2="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <f>_xlfn.IFS(Sheet1!AA2="P", 5,Sheet1!AA2="O", 3,Sheet1!AA2="A",0,Sheet1!AA2="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <f>SUM(B2:AA2)</f>
+        <v>13</v>
+      </c>
+      <c r="AD2">
+        <f>AC2*5/100</f>
+        <v>0.65</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <f>AE2*5/100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f>_xlfn.IFS(Sheet1!B3="P", 5,Sheet1!B3="O", 3,Sheet1!B3="A",0,Sheet1!B3="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <f>_xlfn.IFS(Sheet1!C3="P", 5,Sheet1!C3="O", 3,Sheet1!C3="A",0,Sheet1!C3="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <f>_xlfn.IFS(Sheet1!D3="P", 5,Sheet1!D3="O", 3,Sheet1!D3="A",0,Sheet1!D3="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <f>_xlfn.IFS(Sheet1!E3="P", 5,Sheet1!E3="O", 3,Sheet1!E3="A",0,Sheet1!E3="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <f>_xlfn.IFS(Sheet1!F3="P", 5,Sheet1!F3="O", 3,Sheet1!F3="A",0,Sheet1!F3="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <f>_xlfn.IFS(Sheet1!G3="P", 5,Sheet1!G3="O", 3,Sheet1!G3="A",0,Sheet1!G3="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <f>_xlfn.IFS(Sheet1!H3="P", 5,Sheet1!H3="O", 3,Sheet1!H3="A",0,Sheet1!H3="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <f>_xlfn.IFS(Sheet1!I3="P", 5,Sheet1!I3="O", 3,Sheet1!I3="A",0,Sheet1!I3="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <f>_xlfn.IFS(Sheet1!J3="P", 5,Sheet1!J3="O", 3,Sheet1!J3="A",0,Sheet1!J3="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <f>_xlfn.IFS(Sheet1!K3="P", 5,Sheet1!K3="O", 3,Sheet1!K3="A",0,Sheet1!K3="-",0)</f>
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <f>_xlfn.IFS(Sheet1!L3="P", 5,Sheet1!L3="O", 3,Sheet1!L3="A",0,Sheet1!L3="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <f>_xlfn.IFS(Sheet1!M3="P", 5,Sheet1!M3="O", 3,Sheet1!M3="A",0,Sheet1!M3="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N3">
+        <f>_xlfn.IFS(Sheet1!N3="P", 5,Sheet1!N3="O", 3,Sheet1!N3="A",0,Sheet1!N3="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O3">
+        <f>_xlfn.IFS(Sheet1!O3="P", 5,Sheet1!O3="O", 3,Sheet1!O3="A",0,Sheet1!O3="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="P3">
+        <f>_xlfn.IFS(Sheet1!P3="P", 5,Sheet1!P3="O", 3,Sheet1!P3="A",0,Sheet1!P3="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Q3">
+        <f>_xlfn.IFS(Sheet1!Q3="P", 5,Sheet1!Q3="O", 3,Sheet1!Q3="A",0,Sheet1!Q3="-",0)</f>
+        <v>3</v>
+      </c>
+      <c r="R3">
+        <f>_xlfn.IFS(Sheet1!R3="P", 5,Sheet1!R3="O", 3,Sheet1!R3="A",0,Sheet1!R3="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="S3">
+        <f>_xlfn.IFS(Sheet1!S3="P", 5,Sheet1!S3="O", 3,Sheet1!S3="A",0,Sheet1!S3="-",0)</f>
+        <v>3</v>
+      </c>
+      <c r="T3">
+        <f>_xlfn.IFS(Sheet1!T3="P", 5,Sheet1!T3="O", 3,Sheet1!T3="A",0,Sheet1!T3="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="U3">
+        <f>_xlfn.IFS(Sheet1!U3="P", 5,Sheet1!U3="O", 3,Sheet1!U3="A",0,Sheet1!U3="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="V3">
+        <f>_xlfn.IFS(Sheet1!V3="P", 5,Sheet1!V3="O", 3,Sheet1!V3="A",0,Sheet1!V3="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="W3">
+        <f>_xlfn.IFS(Sheet1!W3="P", 5,Sheet1!W3="O", 3,Sheet1!W3="A",0,Sheet1!W3="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="X3">
+        <f>_xlfn.IFS(Sheet1!X3="P", 5,Sheet1!X3="O", 3,Sheet1!X3="A",0,Sheet1!X3="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Y3">
+        <f>_xlfn.IFS(Sheet1!Y3="P", 5,Sheet1!Y3="O", 3,Sheet1!Y3="A",0,Sheet1!Y3="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Z3">
+        <f>_xlfn.IFS(Sheet1!Z3="P", 5,Sheet1!Z3="O", 3,Sheet1!Z3="A",0,Sheet1!Z3="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="AA3">
+        <f>_xlfn.IFS(Sheet1!AA3="P", 5,Sheet1!AA3="O", 3,Sheet1!AA3="A",0,Sheet1!AA3="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="AC3">
+        <f t="shared" ref="AC3:AC7" si="0">SUM(B3:AA3)</f>
+        <v>104</v>
+      </c>
+      <c r="AD3">
+        <f t="shared" ref="AD3:AD7" si="1">AC3*5/100</f>
+        <v>5.2</v>
+      </c>
+      <c r="AE3">
+        <v>90</v>
+      </c>
+      <c r="AF3">
+        <f t="shared" ref="AF3:AF7" si="2">AE3*5/100</f>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <f>_xlfn.IFS(Sheet1!B4="P", 5,Sheet1!B4="O", 3,Sheet1!B4="A",0,Sheet1!B4="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <f>_xlfn.IFS(Sheet1!C4="P", 5,Sheet1!C4="O", 3,Sheet1!C4="A",0,Sheet1!C4="-",0)</f>
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <f>_xlfn.IFS(Sheet1!D4="P", 5,Sheet1!D4="O", 3,Sheet1!D4="A",0,Sheet1!D4="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <f>_xlfn.IFS(Sheet1!E4="P", 5,Sheet1!E4="O", 3,Sheet1!E4="A",0,Sheet1!E4="-",0)</f>
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <f>_xlfn.IFS(Sheet1!F4="P", 5,Sheet1!F4="O", 3,Sheet1!F4="A",0,Sheet1!F4="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G4">
+        <f>_xlfn.IFS(Sheet1!G4="P", 5,Sheet1!G4="O", 3,Sheet1!G4="A",0,Sheet1!G4="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <f>_xlfn.IFS(Sheet1!H4="P", 5,Sheet1!H4="O", 3,Sheet1!H4="A",0,Sheet1!H4="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <f>_xlfn.IFS(Sheet1!I4="P", 5,Sheet1!I4="O", 3,Sheet1!I4="A",0,Sheet1!I4="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J4">
+        <f>_xlfn.IFS(Sheet1!J4="P", 5,Sheet1!J4="O", 3,Sheet1!J4="A",0,Sheet1!J4="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <f>_xlfn.IFS(Sheet1!K4="P", 5,Sheet1!K4="O", 3,Sheet1!K4="A",0,Sheet1!K4="-",0)</f>
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <f>_xlfn.IFS(Sheet1!L4="P", 5,Sheet1!L4="O", 3,Sheet1!L4="A",0,Sheet1!L4="-",0)</f>
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <f>_xlfn.IFS(Sheet1!M4="P", 5,Sheet1!M4="O", 3,Sheet1!M4="A",0,Sheet1!M4="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <f>_xlfn.IFS(Sheet1!N4="P", 5,Sheet1!N4="O", 3,Sheet1!N4="A",0,Sheet1!N4="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <f>_xlfn.IFS(Sheet1!O4="P", 5,Sheet1!O4="O", 3,Sheet1!O4="A",0,Sheet1!O4="-",0)</f>
+        <v>3</v>
+      </c>
+      <c r="P4">
+        <f>_xlfn.IFS(Sheet1!P4="P", 5,Sheet1!P4="O", 3,Sheet1!P4="A",0,Sheet1!P4="-",0)</f>
+        <v>3</v>
+      </c>
+      <c r="Q4">
+        <f>_xlfn.IFS(Sheet1!Q4="P", 5,Sheet1!Q4="O", 3,Sheet1!Q4="A",0,Sheet1!Q4="-",0)</f>
+        <v>3</v>
+      </c>
+      <c r="R4">
+        <f>_xlfn.IFS(Sheet1!R4="P", 5,Sheet1!R4="O", 3,Sheet1!R4="A",0,Sheet1!R4="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <f>_xlfn.IFS(Sheet1!S4="P", 5,Sheet1!S4="O", 3,Sheet1!S4="A",0,Sheet1!S4="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <f>_xlfn.IFS(Sheet1!T4="P", 5,Sheet1!T4="O", 3,Sheet1!T4="A",0,Sheet1!T4="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <f>_xlfn.IFS(Sheet1!U4="P", 5,Sheet1!U4="O", 3,Sheet1!U4="A",0,Sheet1!U4="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <f>_xlfn.IFS(Sheet1!V4="P", 5,Sheet1!V4="O", 3,Sheet1!V4="A",0,Sheet1!V4="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <f>_xlfn.IFS(Sheet1!W4="P", 5,Sheet1!W4="O", 3,Sheet1!W4="A",0,Sheet1!W4="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.IFS(Sheet1!X4="P", 5,Sheet1!X4="O", 3,Sheet1!X4="A",0,Sheet1!X4="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <f>_xlfn.IFS(Sheet1!Y4="P", 5,Sheet1!Y4="O", 3,Sheet1!Y4="A",0,Sheet1!Y4="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.IFS(Sheet1!Z4="P", 5,Sheet1!Z4="O", 3,Sheet1!Z4="A",0,Sheet1!Z4="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <f>_xlfn.IFS(Sheet1!AA4="P", 5,Sheet1!AA4="O", 3,Sheet1!AA4="A",0,Sheet1!AA4="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="AD4">
+        <f t="shared" si="1"/>
+        <v>2.8</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <f>_xlfn.IFS(Sheet1!B5="P", 5,Sheet1!B5="O", 3,Sheet1!B5="A",0,Sheet1!B5="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <f>_xlfn.IFS(Sheet1!C5="P", 5,Sheet1!C5="O", 3,Sheet1!C5="A",0,Sheet1!C5="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <f>_xlfn.IFS(Sheet1!D5="P", 5,Sheet1!D5="O", 3,Sheet1!D5="A",0,Sheet1!D5="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <f>_xlfn.IFS(Sheet1!E5="P", 5,Sheet1!E5="O", 3,Sheet1!E5="A",0,Sheet1!E5="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <f>_xlfn.IFS(Sheet1!F5="P", 5,Sheet1!F5="O", 3,Sheet1!F5="A",0,Sheet1!F5="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <f>_xlfn.IFS(Sheet1!G5="P", 5,Sheet1!G5="O", 3,Sheet1!G5="A",0,Sheet1!G5="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <f>_xlfn.IFS(Sheet1!H5="P", 5,Sheet1!H5="O", 3,Sheet1!H5="A",0,Sheet1!H5="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <f>_xlfn.IFS(Sheet1!I5="P", 5,Sheet1!I5="O", 3,Sheet1!I5="A",0,Sheet1!I5="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <f>_xlfn.IFS(Sheet1!J5="P", 5,Sheet1!J5="O", 3,Sheet1!J5="A",0,Sheet1!J5="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <f>_xlfn.IFS(Sheet1!K5="P", 5,Sheet1!K5="O", 3,Sheet1!K5="A",0,Sheet1!K5="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <f>_xlfn.IFS(Sheet1!L5="P", 5,Sheet1!L5="O", 3,Sheet1!L5="A",0,Sheet1!L5="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <f>_xlfn.IFS(Sheet1!M5="P", 5,Sheet1!M5="O", 3,Sheet1!M5="A",0,Sheet1!M5="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N5">
+        <f>_xlfn.IFS(Sheet1!N5="P", 5,Sheet1!N5="O", 3,Sheet1!N5="A",0,Sheet1!N5="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O5">
+        <f>_xlfn.IFS(Sheet1!O5="P", 5,Sheet1!O5="O", 3,Sheet1!O5="A",0,Sheet1!O5="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="P5">
+        <f>_xlfn.IFS(Sheet1!P5="P", 5,Sheet1!P5="O", 3,Sheet1!P5="A",0,Sheet1!P5="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <f>_xlfn.IFS(Sheet1!Q5="P", 5,Sheet1!Q5="O", 3,Sheet1!Q5="A",0,Sheet1!Q5="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <f>_xlfn.IFS(Sheet1!R5="P", 5,Sheet1!R5="O", 3,Sheet1!R5="A",0,Sheet1!R5="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="S5">
+        <f>_xlfn.IFS(Sheet1!S5="P", 5,Sheet1!S5="O", 3,Sheet1!S5="A",0,Sheet1!S5="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <f>_xlfn.IFS(Sheet1!T5="P", 5,Sheet1!T5="O", 3,Sheet1!T5="A",0,Sheet1!T5="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="U5">
+        <f>_xlfn.IFS(Sheet1!U5="P", 5,Sheet1!U5="O", 3,Sheet1!U5="A",0,Sheet1!U5="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="V5">
+        <f>_xlfn.IFS(Sheet1!V5="P", 5,Sheet1!V5="O", 3,Sheet1!V5="A",0,Sheet1!V5="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="W5">
+        <f>_xlfn.IFS(Sheet1!W5="P", 5,Sheet1!W5="O", 3,Sheet1!W5="A",0,Sheet1!W5="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="X5">
+        <f>_xlfn.IFS(Sheet1!X5="P", 5,Sheet1!X5="O", 3,Sheet1!X5="A",0,Sheet1!X5="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <f>_xlfn.IFS(Sheet1!Y5="P", 5,Sheet1!Y5="O", 3,Sheet1!Y5="A",0,Sheet1!Y5="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <f>_xlfn.IFS(Sheet1!Z5="P", 5,Sheet1!Z5="O", 3,Sheet1!Z5="A",0,Sheet1!Z5="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <f>_xlfn.IFS(Sheet1!AA5="P", 5,Sheet1!AA5="O", 3,Sheet1!AA5="A",0,Sheet1!AA5="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" si="1"/>
+        <v>4.5</v>
+      </c>
+      <c r="AE5">
+        <v>90</v>
+      </c>
+      <c r="AF5">
+        <f t="shared" si="2"/>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <f>_xlfn.IFS(Sheet1!B6="P", 5,Sheet1!B6="O", 3,Sheet1!B6="A",0,Sheet1!B6="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <f>_xlfn.IFS(Sheet1!C6="P", 5,Sheet1!C6="O", 3,Sheet1!C6="A",0,Sheet1!C6="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <f>_xlfn.IFS(Sheet1!D6="P", 5,Sheet1!D6="O", 3,Sheet1!D6="A",0,Sheet1!D6="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <f>_xlfn.IFS(Sheet1!E6="P", 5,Sheet1!E6="O", 3,Sheet1!E6="A",0,Sheet1!E6="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <f>_xlfn.IFS(Sheet1!F6="P", 5,Sheet1!F6="O", 3,Sheet1!F6="A",0,Sheet1!F6="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <f>_xlfn.IFS(Sheet1!G6="P", 5,Sheet1!G6="O", 3,Sheet1!G6="A",0,Sheet1!G6="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <f>_xlfn.IFS(Sheet1!H6="P", 5,Sheet1!H6="O", 3,Sheet1!H6="A",0,Sheet1!H6="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <f>_xlfn.IFS(Sheet1!I6="P", 5,Sheet1!I6="O", 3,Sheet1!I6="A",0,Sheet1!I6="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <f>_xlfn.IFS(Sheet1!J6="P", 5,Sheet1!J6="O", 3,Sheet1!J6="A",0,Sheet1!J6="-",0)</f>
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <f>_xlfn.IFS(Sheet1!K6="P", 5,Sheet1!K6="O", 3,Sheet1!K6="A",0,Sheet1!K6="-",0)</f>
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <f>_xlfn.IFS(Sheet1!L6="P", 5,Sheet1!L6="O", 3,Sheet1!L6="A",0,Sheet1!L6="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <f>_xlfn.IFS(Sheet1!M6="P", 5,Sheet1!M6="O", 3,Sheet1!M6="A",0,Sheet1!M6="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N6">
+        <f>_xlfn.IFS(Sheet1!N6="P", 5,Sheet1!N6="O", 3,Sheet1!N6="A",0,Sheet1!N6="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O6">
+        <f>_xlfn.IFS(Sheet1!O6="P", 5,Sheet1!O6="O", 3,Sheet1!O6="A",0,Sheet1!O6="-",0)</f>
+        <v>3</v>
+      </c>
+      <c r="P6">
+        <f>_xlfn.IFS(Sheet1!P6="P", 5,Sheet1!P6="O", 3,Sheet1!P6="A",0,Sheet1!P6="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Q6">
+        <f>_xlfn.IFS(Sheet1!Q6="P", 5,Sheet1!Q6="O", 3,Sheet1!Q6="A",0,Sheet1!Q6="-",0)</f>
+        <v>3</v>
+      </c>
+      <c r="R6">
+        <f>_xlfn.IFS(Sheet1!R6="P", 5,Sheet1!R6="O", 3,Sheet1!R6="A",0,Sheet1!R6="-",0)</f>
+        <v>3</v>
+      </c>
+      <c r="S6">
+        <f>_xlfn.IFS(Sheet1!S6="P", 5,Sheet1!S6="O", 3,Sheet1!S6="A",0,Sheet1!S6="-",0)</f>
+        <v>3</v>
+      </c>
+      <c r="T6">
+        <f>_xlfn.IFS(Sheet1!T6="P", 5,Sheet1!T6="O", 3,Sheet1!T6="A",0,Sheet1!T6="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="U6">
+        <f>_xlfn.IFS(Sheet1!U6="P", 5,Sheet1!U6="O", 3,Sheet1!U6="A",0,Sheet1!U6="-",0)</f>
+        <v>3</v>
+      </c>
+      <c r="V6">
+        <f>_xlfn.IFS(Sheet1!V6="P", 5,Sheet1!V6="O", 3,Sheet1!V6="A",0,Sheet1!V6="-",0)</f>
+        <v>3</v>
+      </c>
+      <c r="W6">
+        <f>_xlfn.IFS(Sheet1!W6="P", 5,Sheet1!W6="O", 3,Sheet1!W6="A",0,Sheet1!W6="-",0)</f>
+        <v>3</v>
+      </c>
+      <c r="X6">
+        <f>_xlfn.IFS(Sheet1!X6="P", 5,Sheet1!X6="O", 3,Sheet1!X6="A",0,Sheet1!X6="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Y6">
+        <f>_xlfn.IFS(Sheet1!Y6="P", 5,Sheet1!Y6="O", 3,Sheet1!Y6="A",0,Sheet1!Y6="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Z6">
+        <f>_xlfn.IFS(Sheet1!Z6="P", 5,Sheet1!Z6="O", 3,Sheet1!Z6="A",0,Sheet1!Z6="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="AA6">
+        <f>_xlfn.IFS(Sheet1!AA6="P", 5,Sheet1!AA6="O", 3,Sheet1!AA6="A",0,Sheet1!AA6="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="0"/>
+        <v>102</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="1"/>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="AE6">
+        <v>90</v>
+      </c>
+      <c r="AF6">
+        <f t="shared" si="2"/>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <f>_xlfn.IFS(Sheet1!B7="P", 5,Sheet1!B7="O", 3,Sheet1!B7="A",0,Sheet1!B7="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <f>_xlfn.IFS(Sheet1!C7="P", 5,Sheet1!C7="O", 3,Sheet1!C7="A",0,Sheet1!C7="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <f>_xlfn.IFS(Sheet1!D7="P", 5,Sheet1!D7="O", 3,Sheet1!D7="A",0,Sheet1!D7="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <f>_xlfn.IFS(Sheet1!E7="P", 5,Sheet1!E7="O", 3,Sheet1!E7="A",0,Sheet1!E7="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <f>_xlfn.IFS(Sheet1!F7="P", 5,Sheet1!F7="O", 3,Sheet1!F7="A",0,Sheet1!F7="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <f>_xlfn.IFS(Sheet1!G7="P", 5,Sheet1!G7="O", 3,Sheet1!G7="A",0,Sheet1!G7="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <f>_xlfn.IFS(Sheet1!H7="P", 5,Sheet1!H7="O", 3,Sheet1!H7="A",0,Sheet1!H7="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <f>_xlfn.IFS(Sheet1!I7="P", 5,Sheet1!I7="O", 3,Sheet1!I7="A",0,Sheet1!I7="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <f>_xlfn.IFS(Sheet1!J7="P", 5,Sheet1!J7="O", 3,Sheet1!J7="A",0,Sheet1!J7="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <f>_xlfn.IFS(Sheet1!K7="P", 5,Sheet1!K7="O", 3,Sheet1!K7="A",0,Sheet1!K7="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <f>_xlfn.IFS(Sheet1!L7="P", 5,Sheet1!L7="O", 3,Sheet1!L7="A",0,Sheet1!L7="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <f>_xlfn.IFS(Sheet1!M7="P", 5,Sheet1!M7="O", 3,Sheet1!M7="A",0,Sheet1!M7="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <f>_xlfn.IFS(Sheet1!N7="P", 5,Sheet1!N7="O", 3,Sheet1!N7="A",0,Sheet1!N7="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <f>_xlfn.IFS(Sheet1!O7="P", 5,Sheet1!O7="O", 3,Sheet1!O7="A",0,Sheet1!O7="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <f>_xlfn.IFS(Sheet1!P7="P", 5,Sheet1!P7="O", 3,Sheet1!P7="A",0,Sheet1!P7="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <f>_xlfn.IFS(Sheet1!Q7="P", 5,Sheet1!Q7="O", 3,Sheet1!Q7="A",0,Sheet1!Q7="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <f>_xlfn.IFS(Sheet1!R7="P", 5,Sheet1!R7="O", 3,Sheet1!R7="A",0,Sheet1!R7="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <f>_xlfn.IFS(Sheet1!S7="P", 5,Sheet1!S7="O", 3,Sheet1!S7="A",0,Sheet1!S7="-",0)</f>
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <f>_xlfn.IFS(Sheet1!T7="P", 5,Sheet1!T7="O", 3,Sheet1!T7="A",0,Sheet1!T7="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="U7">
+        <f>_xlfn.IFS(Sheet1!U7="P", 5,Sheet1!U7="O", 3,Sheet1!U7="A",0,Sheet1!U7="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="V7">
+        <f>_xlfn.IFS(Sheet1!V7="P", 5,Sheet1!V7="O", 3,Sheet1!V7="A",0,Sheet1!V7="-",0)</f>
+        <v>3</v>
+      </c>
+      <c r="W7">
+        <f>_xlfn.IFS(Sheet1!W7="P", 5,Sheet1!W7="O", 3,Sheet1!W7="A",0,Sheet1!W7="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="X7">
+        <f>_xlfn.IFS(Sheet1!X7="P", 5,Sheet1!X7="O", 3,Sheet1!X7="A",0,Sheet1!X7="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Y7">
+        <f>_xlfn.IFS(Sheet1!Y7="P", 5,Sheet1!Y7="O", 3,Sheet1!Y7="A",0,Sheet1!Y7="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Z7">
+        <f>_xlfn.IFS(Sheet1!Z7="P", 5,Sheet1!Z7="O", 3,Sheet1!Z7="A",0,Sheet1!Z7="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="AA7">
+        <f>_xlfn.IFS(Sheet1!AA7="P", 5,Sheet1!AA7="O", 3,Sheet1!AA7="A",0,Sheet1!AA7="-",0)</f>
+        <v>5</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="1"/>
+        <v>1.9</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/21Club_Sept_CW1/DS/Attendance.xlsx
+++ b/21Club_Sept_CW1/DS/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\21Club_Sept_CW1\DS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F46AD40-D1E7-4BD5-B7DB-6E280DC48090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C306CBED-74D0-4D24-98F6-3233A5379B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="15">
   <si>
     <t>Vedant</t>
   </si>
@@ -389,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB16"/>
+  <dimension ref="A1:AD16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
@@ -404,7 +404,7 @@
     <col min="24" max="24" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B1" s="1">
         <v>45437</v>
       </c>
@@ -486,8 +486,14 @@
       <c r="AB1" s="1">
         <v>45591</v>
       </c>
+      <c r="AC1" s="1">
+        <v>45605</v>
+      </c>
+      <c r="AD1" s="1">
+        <v>45612</v>
+      </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -572,8 +578,11 @@
       <c r="AB2" t="s">
         <v>8</v>
       </c>
+      <c r="AC2" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -658,8 +667,14 @@
       <c r="AB3" t="s">
         <v>6</v>
       </c>
+      <c r="AC3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -744,8 +759,11 @@
       <c r="AB4" t="s">
         <v>8</v>
       </c>
+      <c r="AC4" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -830,8 +848,14 @@
       <c r="AB5" t="s">
         <v>6</v>
       </c>
+      <c r="AC5" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -916,8 +940,14 @@
       <c r="AB6" t="s">
         <v>7</v>
       </c>
+      <c r="AC6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1002,13 +1032,19 @@
       <c r="AB7" t="s">
         <v>7</v>
       </c>
+      <c r="AC7" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="K16">
         <v>22</v>
       </c>

--- a/21Club_Sept_CW1/DS/Attendance.xlsx
+++ b/21Club_Sept_CW1/DS/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\21Club_Sept_CW1\DS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C306CBED-74D0-4D24-98F6-3233A5379B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90DD13B1-CB19-4DF7-9A14-306E6118104C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="15">
   <si>
     <t>Vedant</t>
   </si>
@@ -389,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD16"/>
+  <dimension ref="A1:AE16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
@@ -404,7 +404,7 @@
     <col min="24" max="24" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B1" s="1">
         <v>45437</v>
       </c>
@@ -492,8 +492,11 @@
       <c r="AD1" s="1">
         <v>45612</v>
       </c>
+      <c r="AE1" s="1">
+        <v>45613</v>
+      </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -582,7 +585,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -673,8 +676,11 @@
       <c r="AD3" t="s">
         <v>6</v>
       </c>
+      <c r="AE3" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -763,7 +769,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -854,8 +860,11 @@
       <c r="AD5" t="s">
         <v>6</v>
       </c>
+      <c r="AE5" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -946,8 +955,11 @@
       <c r="AD6" t="s">
         <v>7</v>
       </c>
+      <c r="AE6" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1038,13 +1050,16 @@
       <c r="AD7" t="s">
         <v>5</v>
       </c>
+      <c r="AE7" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="K16">
         <v>22</v>
       </c>

--- a/21Club_Sept_CW1/DS/Attendance.xlsx
+++ b/21Club_Sept_CW1/DS/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\21Club_Sept_CW1\DS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90DD13B1-CB19-4DF7-9A14-306E6118104C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4FA26E4-1D7C-491B-BABC-969D92930CC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="15">
   <si>
     <t>Vedant</t>
   </si>
@@ -389,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE16"/>
+  <dimension ref="A1:AF16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
@@ -404,7 +404,7 @@
     <col min="24" max="24" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B1" s="1">
         <v>45437</v>
       </c>
@@ -495,8 +495,11 @@
       <c r="AE1" s="1">
         <v>45613</v>
       </c>
+      <c r="AF1" s="1">
+        <v>45619</v>
+      </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -585,7 +588,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -679,8 +682,11 @@
       <c r="AE3" t="s">
         <v>6</v>
       </c>
+      <c r="AF3" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -769,7 +775,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -863,8 +869,11 @@
       <c r="AE5" t="s">
         <v>5</v>
       </c>
+      <c r="AF5" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -958,8 +967,11 @@
       <c r="AE6" t="s">
         <v>6</v>
       </c>
+      <c r="AF6" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1053,13 +1065,16 @@
       <c r="AE7" t="s">
         <v>5</v>
       </c>
+      <c r="AF7" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
       <c r="K16">
         <v>22</v>
       </c>
